--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488015_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488015_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6074</v>
+        <v>5.5522</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4872</v>
+        <v>4.797</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1202</v>
+        <v>0.7552</v>
       </c>
       <c r="G2" t="n">
         <v>5.9466</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>1.401</v>
+        <v>0.3459</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1014</v>
+        <v>0.4113</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2996</v>
+        <v>-0.0654</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1367</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9534</v>
+        <v>4.969</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9803</v>
+        <v>6.024</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0269</v>
+        <v>-1.0549</v>
       </c>
       <c r="G3" t="n">
         <v>4.6435</v>
@@ -688,13 +688,13 @@
         <v>0.5947</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4555</v>
+        <v>1.4711</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2394</v>
+        <v>1.2831</v>
       </c>
       <c r="U3" t="n">
-        <v>0.216</v>
+        <v>0.188</v>
       </c>
       <c r="V3" t="n">
         <v>-1.7403</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VIVAR MARTINEZ</t>
+          <t>T. ESTEVES VEHVILAINEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8358</v>
+        <v>4.6489</v>
       </c>
       <c r="E4" t="n">
-        <v>1.221</v>
+        <v>3.9561</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6148</v>
+        <v>0.6928</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6061</v>
+        <v>1.9189</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4454</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1607</v>
+        <v>1.9189</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0222</v>
+        <v>1.6747</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6935</v>
+        <v>-0.2214</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6713</v>
+        <v>1.8961</v>
       </c>
       <c r="M4" t="n">
-        <v>0.584</v>
+        <v>0.2442</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2481</v>
+        <v>0.2214</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8321</v>
+        <v>0.0228</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4689</v>
+        <v>0.2652</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3192</v>
+        <v>0.8077</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1496</v>
+        <v>-0.5425</v>
       </c>
       <c r="V4" t="n">
-        <v>4.4914</v>
+        <v>1.4737</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4914</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. ESTEVES VEHVILAINEN</t>
+          <t>L. VIVAR MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0552</v>
+        <v>4.1715</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6713</v>
+        <v>1.7533</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3839</v>
+        <v>2.4182</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9189</v>
+        <v>0.6061</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0.4454</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9189</v>
+        <v>0.1607</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6747</v>
+        <v>0.0222</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2214</v>
+        <v>0.6935</v>
       </c>
       <c r="L5" t="n">
-        <v>1.8961</v>
+        <v>-0.6713</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2442</v>
+        <v>0.584</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2214</v>
+        <v>-0.2481</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0228</v>
+        <v>0.8321</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3285</v>
+        <v>-0.1332</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4771</v>
+        <v>0.213</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8514</v>
+        <v>-0.3462</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4737</v>
+        <v>4.4914</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>4.4914</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3632</v>
+        <v>2.3238</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9587</v>
+        <v>1.9192</v>
       </c>
       <c r="F6" t="n">
         <v>0.4045</v>
@@ -922,10 +922,10 @@
         <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8158</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2423</v>
+        <v>0.2029</v>
       </c>
       <c r="U6" t="n">
         <v>0.6129</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9226</v>
+        <v>1.037</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4924</v>
+        <v>1.7191</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5698</v>
+        <v>-0.6821</v>
       </c>
       <c r="G7" t="n">
         <v>0.2008</v>
@@ -1000,13 +1000,13 @@
         <v>0.9911</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8428</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.8582</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2113</v>
+        <v>0.0989</v>
       </c>
       <c r="V7" t="n">
         <v>0.8701</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5579</v>
+        <v>-0.1116</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0519</v>
+        <v>-0.4773</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6098</v>
+        <v>0.3657</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7742</v>
+        <v>0.8203</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.07140000000000001</v>
+        <v>1.4862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8455</v>
+        <v>-0.6659</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4808</v>
+        <v>1.1836</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1147</v>
+        <v>1.7422</v>
       </c>
       <c r="L9" t="n">
-        <v>1.366</v>
+        <v>-0.5586</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7066</v>
+        <v>-0.3633</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1861</v>
+        <v>-0.256</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5205</v>
+        <v>-0.1073</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.9822</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.9733</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.9911</v>
+        <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7065</v>
+        <v>-0.1322</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1146</v>
+        <v>0.3213</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5919</v>
+        <v>-0.4535</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>-0.7997</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2666</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MARTIN ARROYO</t>
+          <t>J. PAEZ AVILA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5616</v>
+        <v>-0.7554</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1108</v>
+        <v>-0.7517</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4508</v>
+        <v>-0.0037</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.8871</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6254999999999999</v>
+        <v>-1.2766</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3469</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0536</v>
+        <v>-0.4372</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6254999999999999</v>
+        <v>-0.4774</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6791</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6677</v>
+        <v>-1.4499</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.7993</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6677</v>
+        <v>-0.6506</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6355</v>
+        <v>-0.135</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6167</v>
+        <v>-0.1936</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0187</v>
+        <v>0.0586</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.674</v>
+        <v>0.8701</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.674</v>
+        <v>0.8701</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7209</v>
+        <v>-0.8757</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-1.0082</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1325</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8203</v>
+        <v>0.7742</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4862</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6659</v>
+        <v>0.8455</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1836</v>
+        <v>1.4808</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7422</v>
+        <v>0.1147</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5586</v>
+        <v>1.366</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3633</v>
+        <v>-0.7066</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.256</v>
+        <v>-0.1861</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1073</v>
+        <v>-0.5205</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9822</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7415</v>
+        <v>1.2729</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0072</v>
+        <v>1.1583</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7343</v>
+        <v>0.1145</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7997</v>
+        <v>-0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7997</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. PAEZ AVILA</t>
+          <t>I. MARTIN ARROYO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2982</v>
+        <v>-0.8786</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1821</v>
+        <v>-0.4559</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.116</v>
+        <v>-0.4227</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8871</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2766</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.3469</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4372</v>
+        <v>-0.0536</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4774</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0402</v>
+        <v>-0.6791</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4499</v>
+        <v>-0.6677</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7993</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6506</v>
+        <v>-0.6677</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3876</v>
+        <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6777</v>
+        <v>0.3184</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.624</v>
+        <v>0.2717</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0537</v>
+        <v>0.0468</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8701</v>
+        <v>-0.674</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8701</v>
+        <v>-0.674</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5641</v>
+        <v>-1.8582</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0011</v>
+        <v>-1.4918</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.3664</v>
       </c>
       <c r="G13" t="n">
         <v>2.122</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4967</v>
+        <v>0.2092</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0514</v>
+        <v>0.458</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4454</v>
+        <v>-0.2488</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8107</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.5843</v>
+        <v>-5.7204</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.4529</v>
+        <v>-2.8417</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1314</v>
+        <v>-2.8787</v>
       </c>
       <c r="G14" t="n">
         <v>-1.0927</v>
@@ -1546,13 +1546,13 @@
         <v>1.1893</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7514</v>
+        <v>-0.8874</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6753</v>
+        <v>-0.0641</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.076</v>
+        <v>-0.8233</v>
       </c>
       <c r="V14" t="n">
         <v>-2.9474</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.1717</v>
+        <v>13.1078</v>
       </c>
       <c r="E15" t="n">
-        <v>12.8115</v>
+        <v>13.7474</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6397000000000004</v>
+        <v>-0.6395999999999997</v>
       </c>
       <c r="G15" t="n">
         <v>15.5307</v>
@@ -1594,7 +1594,7 @@
         <v>14.823</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7074999999999998</v>
+        <v>0.7075000000000002</v>
       </c>
       <c r="J15" t="n">
         <v>19.50219999999999</v>
@@ -1603,10 +1603,10 @@
         <v>16.3345</v>
       </c>
       <c r="L15" t="n">
-        <v>3.167799999999999</v>
+        <v>3.1678</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.971400000000001</v>
+        <v>-3.9714</v>
       </c>
       <c r="N15" t="n">
         <v>-1.5115</v>
@@ -1624,10 +1624,10 @@
         <v>14.8668</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4319</v>
+        <v>4.367900000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>4.791799999999999</v>
+        <v>5.727799999999999</v>
       </c>
       <c r="U15" t="n">
         <v>-1.36</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4649</v>
+        <v>3.0051</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4806</v>
+        <v>3.4106</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9843</v>
+        <v>-0.4055</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4901</v>
+        <v>-1.2821</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0601</v>
+        <v>-1.5729</v>
       </c>
       <c r="I16" t="n">
-        <v>0.57</v>
+        <v>0.2908</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4144</v>
+        <v>1.3745</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2687</v>
+        <v>0.1614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.2131</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9044</v>
+        <v>-2.6566</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7914</v>
+        <v>-1.7343</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.113</v>
+        <v>-0.9223</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8361</v>
+        <v>-0.4442</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5331</v>
+        <v>-0.5743</v>
       </c>
       <c r="U16" t="n">
-        <v>0.303</v>
+        <v>0.1301</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5331</v>
+        <v>2.9474</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>2.6104</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0116</v>
+        <v>2.8403</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7994</v>
+        <v>2.2582</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2122</v>
+        <v>0.5821</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2821</v>
+        <v>-0.4901</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5729</v>
+        <v>-1.0601</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2908</v>
+        <v>0.57</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3745</v>
+        <v>0.4144</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1614</v>
+        <v>-0.2687</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2131</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6566</v>
+        <v>-0.9044</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7343</v>
+        <v>-0.7914</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9223</v>
+        <v>-0.113</v>
       </c>
       <c r="P17" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4377</v>
+        <v>1.2114</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1855</v>
+        <v>1.3107</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7479</v>
+        <v>-0.0993</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9474</v>
+        <v>0.5331</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6104</v>
+        <v>0.5331</v>
       </c>
       <c r="X17" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2896</v>
+        <v>0.5332</v>
       </c>
       <c r="E18" t="n">
         <v>4.9846</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.695</v>
+        <v>-4.4514</v>
       </c>
       <c r="G18" t="n">
         <v>0.1058</v>
@@ -1858,13 +1858,13 @@
         <v>2.9733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8519</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>0.1765</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0285</v>
+        <v>-0.7849</v>
       </c>
       <c r="V18" t="n">
         <v>2.0269</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8055</v>
+        <v>-0.4287</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9793</v>
+        <v>-2.183</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1738</v>
+        <v>1.7543</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9054</v>
@@ -2014,13 +2014,13 @@
         <v>2.9733</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.385</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7381</v>
+        <v>0.5343</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.123</v>
+        <v>-0.5425</v>
       </c>
       <c r="V20" t="n">
         <v>1.4938</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0997</v>
+        <v>-2.6829</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7925</v>
+        <v>0.1813</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8923</v>
+        <v>-2.8642</v>
       </c>
       <c r="G21" t="n">
         <v>-1.222</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4593</v>
+        <v>-0.1238</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.0607</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2126</v>
+        <v>-0.1845</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9405</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1815</v>
+        <v>-3.0355</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0324</v>
+        <v>-2.523</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1491</v>
+        <v>-0.5124</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5702</v>
@@ -2170,13 +2170,13 @@
         <v>3.1716</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9554</v>
+        <v>-0.8094</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9322</v>
+        <v>-0.4228</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0232</v>
+        <v>-0.3865</v>
       </c>
       <c r="V22" t="n">
         <v>0.1459</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.828</v>
+        <v>-5.5141</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7755</v>
+        <v>-3.4475</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0526</v>
+        <v>-2.0666</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.1044</v>
+        <v>-3.0624</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0861</v>
+        <v>-2.5517</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0182</v>
+        <v>-0.5106000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2538</v>
+        <v>0.5158</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2496</v>
+        <v>0.6532</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5034</v>
+        <v>-0.1374</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.8505</v>
+        <v>-3.5782</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.3357</v>
+        <v>-3.2049</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5148</v>
+        <v>-0.3733</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5947</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5858</v>
+        <v>3.1716</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9201</v>
+        <v>-0.668</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5399</v>
+        <v>0.0012</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.46</v>
+        <v>-0.6692</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3982</v>
+        <v>-0.9908</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3278</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.0232</v>
+        <v>-5.5309</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.568</v>
+        <v>-1.9792</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4552</v>
+        <v>-3.5517</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0624</v>
+        <v>-4.1044</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5517</v>
+        <v>-2.0861</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5106000000000001</v>
+        <v>-2.0182</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5158</v>
+        <v>-1.2538</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6532</v>
+        <v>0.2496</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1374</v>
+        <v>-1.5034</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.5782</v>
+        <v>-2.8505</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.2049</v>
+        <v>-2.3357</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3733</v>
+        <v>-0.5148</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1716</v>
+        <v>1.5858</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1771</v>
+        <v>-0.623</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1194</v>
+        <v>0.3361</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0578</v>
+        <v>-0.9591</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9908</v>
+        <v>-1.3982</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9908</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.1718</v>
+        <v>-10.8135</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6395</v>
+        <v>0.6396000000000019</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.8115</v>
+        <v>-11.453</v>
       </c>
       <c r="G25" t="n">
         <v>-15.5308</v>
@@ -2374,10 +2374,10 @@
         <v>-14.823</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.707600000000001</v>
+        <v>-0.7076000000000002</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9715</v>
+        <v>3.971500000000001</v>
       </c>
       <c r="K25" t="n">
         <v>1.5113</v>
@@ -2404,13 +2404,13 @@
         <v>17.8401</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4318</v>
+        <v>-2.0736</v>
       </c>
       <c r="T25" t="n">
         <v>1.36</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.7918</v>
+        <v>-3.4335</v>
       </c>
       <c r="V25" t="n">
         <v>3.817600000000001</v>
